--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487076_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487076_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3554</v>
+        <v>3.6013</v>
       </c>
       <c r="E2" t="n">
-        <v>2.312</v>
+        <v>2.5311</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0434</v>
+        <v>1.0702</v>
       </c>
       <c r="G2" t="n">
         <v>3.8579</v>
@@ -610,13 +610,13 @@
         <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0112</v>
+        <v>0.2346</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5803</v>
+        <v>-0.3612</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5959</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4912</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3196</v>
+        <v>2.0453</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2837</v>
+        <v>0.4956</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6033</v>
+        <v>1.5498</v>
       </c>
       <c r="G3" t="n">
         <v>1.6135</v>
@@ -688,13 +688,13 @@
         <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4653</v>
+        <v>0.2604</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.9631</v>
+        <v>-1.1838</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4977</v>
+        <v>1.4442</v>
       </c>
       <c r="V3" t="n">
         <v>0.3645</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9385</v>
+        <v>0.4428</v>
       </c>
       <c r="E4" t="n">
-        <v>1.326</v>
+        <v>1.0444</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3874</v>
+        <v>-0.6016</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5011</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1937</v>
+        <v>0.698</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1969</v>
+        <v>-0.4785</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3907</v>
+        <v>1.1765</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1052</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>A. AREVALO NEGUERUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0109</v>
+        <v>-0.192</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8204</v>
+        <v>0.7003</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8095</v>
+        <v>-0.8923</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7095</v>
+        <v>1.3853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4916</v>
+        <v>-0.7411</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.201</v>
+        <v>2.1263</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6656</v>
+        <v>2.1789</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0076</v>
+        <v>-0.5072</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.342</v>
+        <v>2.6861</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.375</v>
+        <v>-0.7936</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5161</v>
+        <v>-0.2338</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.859</v>
+        <v>-0.5598</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4443</v>
+        <v>0.0367</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4707</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9736</v>
+        <v>0.5503</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1318</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.0266</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1052</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. AREVALO NEGUERUELA</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6868</v>
+        <v>-0.6322</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>-1.102</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1868</v>
+        <v>0.4699</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3853</v>
+        <v>-0.9948</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7411</v>
+        <v>1.5028</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1263</v>
+        <v>-2.4976</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1789</v>
+        <v>-1.0892</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5072</v>
+        <v>0.8487</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6861</v>
+        <v>-1.9378</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7936</v>
+        <v>0.0944</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2338</v>
+        <v>0.6542</v>
       </c>
       <c r="O6" t="n">
         <v>-0.5598</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4581</v>
+        <v>0.5377</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7139</v>
+        <v>-0.0129</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2558</v>
+        <v>0.5506</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.228</v>
+        <v>-1.7192</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>-1.7192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9663</v>
+        <v>-1.4227</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0614</v>
+        <v>-1.6433</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0951</v>
+        <v>0.2206</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9948</v>
+        <v>-0.7095</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5028</v>
+        <v>0.4916</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4976</v>
+        <v>-1.201</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0892</v>
+        <v>1.6656</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8487</v>
+        <v>2.0076</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9378</v>
+        <v>-0.342</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0944</v>
+        <v>-2.375</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6542</v>
+        <v>-1.5161</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5598</v>
+        <v>-0.859</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2036</v>
+        <v>1.0325</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0278</v>
+        <v>-0.3523</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1758</v>
+        <v>1.3847</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7192</v>
+        <v>-2.1318</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.0266</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7192</v>
+        <v>-1.1052</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0187</v>
+        <v>-1.4932</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.744</v>
+        <v>-0.924</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2747</v>
+        <v>-0.5692</v>
       </c>
       <c r="G8" t="n">
         <v>1.1241</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1355</v>
+        <v>0.39</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5467</v>
+        <v>-0.7267</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4112</v>
+        <v>1.1167</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2702</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9196</v>
+        <v>-2.5726</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4228</v>
+        <v>1.3415</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3424</v>
+        <v>-3.9141</v>
       </c>
       <c r="G9" t="n">
         <v>-0.198</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2657</v>
+        <v>0.0813</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3437</v>
+        <v>-0.425</v>
       </c>
       <c r="U9" t="n">
-        <v>0.078</v>
+        <v>0.5063</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4559</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.446</v>
+        <v>-4.3191</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5451</v>
+        <v>-0.4449</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9009</v>
+        <v>-3.8742</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1345</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0919</v>
+        <v>0.2188</v>
       </c>
       <c r="T10" t="n">
-        <v>0.074</v>
+        <v>0.1742</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
         <v>-3.4383</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4348</v>
+        <v>-4.5424</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1062</v>
+        <v>1.998699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.540900000000001</v>
+        <v>-6.5409</v>
       </c>
       <c r="G11" t="n">
         <v>5.4429</v>
@@ -1282,7 +1282,7 @@
         <v>4.1398</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3031</v>
+        <v>1.303100000000001</v>
       </c>
       <c r="J11" t="n">
         <v>18.7847</v>
@@ -1291,7 +1291,7 @@
         <v>11.1196</v>
       </c>
       <c r="L11" t="n">
-        <v>7.665</v>
+        <v>7.664999999999998</v>
       </c>
       <c r="M11" t="n">
         <v>-13.3417</v>
@@ -1312,13 +1312,13 @@
         <v>13.5105</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5977</v>
+        <v>3.489999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.7721</v>
+        <v>-3.879799999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>7.369700000000001</v>
+        <v>7.3698</v>
       </c>
       <c r="V11" t="n">
         <v>-13.4753</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.6202</v>
+        <v>6.1146</v>
       </c>
       <c r="E12" t="n">
-        <v>6.6266</v>
+        <v>6.8269</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0064</v>
+        <v>-0.7123</v>
       </c>
       <c r="G12" t="n">
         <v>4.824</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1699</v>
+        <v>-0.6755</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2201</v>
+        <v>-1.0199</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0502</v>
+        <v>0.3443</v>
       </c>
       <c r="V12" t="n">
         <v>4.6682</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4259</v>
+        <v>4.9739</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5192</v>
+        <v>4.7194</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.2544</v>
       </c>
       <c r="G13" t="n">
         <v>0.8937</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0311</v>
+        <v>-0.4832</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4132</v>
+        <v>-1.2129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.382</v>
+        <v>0.7297</v>
       </c>
       <c r="V13" t="n">
         <v>2.8263</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8586</v>
+        <v>2.5047</v>
       </c>
       <c r="E14" t="n">
-        <v>1.235</v>
+        <v>0.9346</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6236</v>
+        <v>1.5701</v>
       </c>
       <c r="G14" t="n">
         <v>0.2976</v>
@@ -1546,13 +1546,13 @@
         <v>0.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2908</v>
+        <v>-0.0631</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2842</v>
+        <v>-0.5846</v>
       </c>
       <c r="U14" t="n">
-        <v>0.575</v>
+        <v>0.5215</v>
       </c>
       <c r="V14" t="n">
         <v>1.8842</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7127</v>
+        <v>1.0806</v>
       </c>
       <c r="E15" t="n">
-        <v>1.329</v>
+        <v>1.4292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6163</v>
+        <v>-0.3486</v>
       </c>
       <c r="G15" t="n">
         <v>1.0247</v>
@@ -1624,13 +1624,13 @@
         <v>0.193</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.505</v>
+        <v>-0.1372</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2829</v>
+        <v>-0.1828</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2221</v>
+        <v>0.0456</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. ELKSNIS</t>
+          <t>T. TAPÉ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.217</v>
+        <v>-0.0018</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0596</v>
+        <v>0.776</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2766</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0203</v>
+        <v>-1.1087</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0105</v>
+        <v>0.6592</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0307</v>
+        <v>-1.7679</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4276</v>
+        <v>1.7607</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1592</v>
+        <v>1.6143</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2685</v>
+        <v>0.1464</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4479</v>
+        <v>-2.8694</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1487</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2992</v>
+        <v>-1.9143</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R16" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2373</v>
+        <v>-0.2561</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3291</v>
+        <v>-0.7036</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5664</v>
+        <v>0.4475</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.5561</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. TAPÉ</t>
+          <t>R. ELKSNIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.289</v>
+        <v>-0.0497</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6758</v>
+        <v>-0.4601</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9648</v>
+        <v>0.4104</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1087</v>
+        <v>-0.0203</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6592</v>
+        <v>0.0105</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7679</v>
+        <v>-0.0307</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7607</v>
+        <v>1.4276</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6143</v>
+        <v>1.1592</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1464</v>
+        <v>0.2685</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8694</v>
+        <v>-1.4479</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-1.1487</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9143</v>
+        <v>-0.2992</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5433</v>
+        <v>-0.0294</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8037</v>
+        <v>-0.7297</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2604</v>
+        <v>0.7003</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5561</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3503</v>
+        <v>-0.1431</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5351</v>
+        <v>0.6353</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8854</v>
+        <v>-0.7783</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6193</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.538</v>
+        <v>-0.3308</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5354</v>
+        <v>-0.4352</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0026</v>
+        <v>0.1044</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4795</v>
+        <v>-0.3526</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0595</v>
+        <v>-0.9594</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>0.6068</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7644</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2941</v>
+        <v>-0.1672</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5354</v>
+        <v>-0.4352</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2413</v>
+        <v>0.268</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7084</v>
+        <v>-0.6816</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0388</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6696</v>
+        <v>-0.6428</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6667999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0416</v>
+        <v>-0.0149</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2291</v>
+        <v>-2.8686</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3079</v>
+        <v>-3.1076</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.239</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2125</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4871</v>
+        <v>-0.1266</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4132</v>
+        <v>-1.2129</v>
       </c>
       <c r="U21" t="n">
-        <v>0.926</v>
+        <v>1.0863</v>
       </c>
       <c r="V21" t="n">
         <v>0.08450000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3436</v>
+        <v>-4.4742</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9142</v>
+        <v>-4.2146</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5706</v>
+        <v>-0.2596</v>
       </c>
       <c r="G22" t="n">
         <v>-5.091</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4845</v>
+        <v>0.3539</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4931</v>
+        <v>-0.7935</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9776</v>
+        <v>1.1474</v>
       </c>
       <c r="V22" t="n">
         <v>1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.434500000000002</v>
+        <v>6.1022</v>
       </c>
       <c r="E23" t="n">
-        <v>6.540699999999998</v>
+        <v>6.5409</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1062</v>
+        <v>-0.4385999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-5.443000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.5105</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5975</v>
+        <v>-1.9301</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.3698</v>
+        <v>-7.369800000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>4.772</v>
+        <v>5.4396</v>
       </c>
       <c r="V23" t="n">
         <v>13.4753</v>
